--- a/configs/causal_triggers.xlsx
+++ b/configs/causal_triggers.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\CausalGraph\configs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{111F1E0E-A97B-46DD-97B8-28E4B5D02AF9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EF645059-C77D-4291-BDCD-41E56B550CE5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{A42B1F03-982C-48FB-B11A-6F1523FCA151}"/>
   </bookViews>

--- a/configs/causal_triggers.xlsx
+++ b/configs/causal_triggers.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C32"/>
+  <dimension ref="A1:C36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -898,6 +898,66 @@
         </is>
       </c>
     </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>56</v>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>nhờ</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>pos</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>57</v>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>góp phần</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>pos</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>58</v>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>thúc đẩy</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>pos</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>59</v>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>do</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>neu</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
